--- a/data/trans_dic/IP31AA_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP31AA_R-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que se cepillan los dientes una o ninguna vez al día</t>
+          <t>Menores que se cepillan los dientes una o ninguna vez al día (tasa de respuesta: 99,35%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>23,69; 38,36</t>
+          <t>23,95; 38,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23,5; 42,6</t>
+          <t>22,55; 42,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26,05; 37,62</t>
+          <t>26,03; 38,11</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>28,14; 41,87</t>
+          <t>28,75; 42,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30,06; 43,05</t>
+          <t>29,31; 41,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30,62; 40,05</t>
+          <t>30,61; 40,11</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30,01; 63,89</t>
+          <t>30,32; 65,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33,26; 47,87</t>
+          <t>33,29; 48,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>34,36; 55,03</t>
+          <t>34,83; 54,08</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,88; 31,28</t>
+          <t>20,26; 31,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25,59; 36,85</t>
+          <t>25,61; 38,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24,85; 33,14</t>
+          <t>24,16; 32,84</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>29,47; 44,16</t>
+          <t>29,43; 42,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>31,8; 38,9</t>
+          <t>31,6; 38,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31,76; 39,5</t>
+          <t>31,97; 38,93</t>
         </is>
       </c>
     </row>
@@ -803,4 +804,454 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que se cepillan los dientes una o ninguna vez al día (tasa de respuesta: 99,35%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>34506</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>42717</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>77224</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>27362; 43671</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>29986; 57005</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>64349; 94215</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>64429</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>87602</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>152031</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>53275; 78537</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>72558; 103656</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>132494; 173613</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>78853</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>73836</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>152690</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>56450; 121857</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>60818; 89431</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>128493; 199490</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>41939</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>54993</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>96932</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>33111; 50918</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>45167; 67404</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>82075; 111576</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>219727</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>259149</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>478876</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>191083; 272967</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>233724; 285727</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>443992; 540616</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>